--- a/Normalisasi_SalesDB_Peserta.xlsx
+++ b/Normalisasi_SalesDB_Peserta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Maganghub\Bootcamp\Latihan-database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Documents/magangan/Latihan-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D262E7-6C58-4441-BB2F-322AF14B6E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD300DA-66BD-E248-8CFD-3C05E8A2E4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="124">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -384,23 +384,19 @@
     <t>Mulai dari hasil 2NF yang sudah kamu koreksi. Salin tabelnya ke area kerja di bawah, lalu perbaiki sesuai aturan tahap ini.</t>
   </si>
   <si>
-    <t>Catatan</t>
-  </si>
-  <si>
-    <t>1. Dapat terjadi ketidakcocokan antara setiap kode produk, nama produk, kode kategori, nama kategori, qty, dan harga satuan karena data tersimpan pada 1 baris yg sama</t>
-  </si>
-  <si>
-    <t>2. Ketika jumlah transaksi sudah sangat banyak akan sulit nantinya melakukan analisis terhadap penjualan yg telah dilakukan karena data tidak tersimpan beraturan</t>
-  </si>
-  <si>
-    <t>3. Ketika nanti cakupan usaha meluas dan ada data tambahan yg perlu disimpan maka akan sulit untuk melakukan update data master karena data saat ini tidak terpisah2 sesuai dengan semestinya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P001
-</t>
-  </si>
-  <si>
-    <t>P005</t>
+    <t>data pelanggan berulang ulang</t>
+  </si>
+  <si>
+    <t>buat query sulit</t>
+  </si>
+  <si>
+    <t>data produk ditulis berulang2 juga </t>
+  </si>
+  <si>
+    <t>namanya bisa tidak konsisten</t>
+  </si>
+  <si>
+    <t>update kalau gnati satu ganti beberapa kolom</t>
   </si>
   <si>
     <t xml:space="preserve">Monitor 24 inci
@@ -420,44 +416,52 @@
     <t>Aksesoris Komputer</t>
   </si>
   <si>
-    <t>Saya menghapus kolom Total Faktur karena total bisa dihitung melalui perhitungan qty dengan harga satuan</t>
-  </si>
-  <si>
-    <t>P004</t>
-  </si>
-  <si>
-    <t>Pulpen Gel (isi 12)</t>
-  </si>
-  <si>
-    <t>K02</t>
-  </si>
-  <si>
-    <t>Alat Tulis</t>
-  </si>
-  <si>
-    <t>P003</t>
-  </si>
-  <si>
-    <t>Buku Catatan A5</t>
+    <t xml:space="preserve">1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.850.000
+</t>
+  </si>
+  <si>
+    <t>kode produk</t>
+  </si>
+  <si>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K03
+</t>
   </si>
   <si>
     <t>P001</t>
   </si>
   <si>
-    <t>Monitor 24 inci</t>
-  </si>
-  <si>
-    <t>P006</t>
+    <t>p005</t>
   </si>
   <si>
     <t>Keyboard Mekanik</t>
   </si>
   <si>
-    <t>No Faktur, Kode Pelanggan</t>
-  </si>
-  <si>
-    <t>No Faktur -&gt; Tanggal, Qty
-Kode Pelanggan -&gt; Nama Pelanggan, Email, Kota</t>
+    <t>AKSESORIS KOMPUTER</t>
+  </si>
+  <si>
+    <t>p002</t>
+  </si>
+  <si>
+    <t>(Kolom A, dan Kolom B) composite key</t>
+  </si>
+  <si>
+    <t>kolom no faktur dan kode produk saya jadikan sebelahan agar mudah dikenali sebagai composite  key, supaya atomic yang satu kolom ada 2 value saya jadikan satu baris, total faktur juga nilainya saya sesuaikan</t>
+  </si>
+  <si>
+    <t>No Faktur  -&gt; Tanggal, Kode Pelanggan, Total Faktur
+Kode Pelanggan -&gt; Nama Pelanggan, Email, Kota
+Kode Produk -&gt; Nama Produk, Harga Satuan, Kode Kategori
+Kode Kategori, Nama Kategorri</t>
   </si>
 </sst>
 </file>
@@ -467,7 +471,7 @@
   <numFmts count="1">
     <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,55 +483,59 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -565,7 +573,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -590,12 +598,29 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
         <color rgb="FFBFBFBF"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -603,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -631,18 +656,30 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -947,124 +984,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
       <c r="B23" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
       <c r="B24" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
         <v>19</v>
       </c>
@@ -1076,8 +1113,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1087,23 +1124,23 @@
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="26.7109375" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>22</v>
       </c>
@@ -1144,7 +1181,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>35</v>
       </c>
@@ -1185,7 +1222,7 @@
         <v>2150000</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>46</v>
       </c>
@@ -1226,7 +1263,7 @@
         <v>900000</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>57</v>
       </c>
@@ -1267,7 +1304,7 @@
         <v>1050000</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>68</v>
       </c>
@@ -1308,7 +1345,7 @@
         <v>346000</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>75</v>
       </c>
@@ -1349,7 +1386,7 @@
         <v>548000</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>82</v>
       </c>
@@ -1390,24 +1427,27 @@
         <v>4450000</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="19" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
         <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="19" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1418,288 +1458,296 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" customWidth="1"/>
-    <col min="10" max="10" width="22.28515625" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" customWidth="1"/>
+    <col min="14" max="14" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>122</v>
+      <c r="B6" s="28" t="s">
+        <v>121</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="29" t="s">
         <v>123</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:13" ht="45" x14ac:dyDescent="0.2">
+      <c r="A11" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="F11" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="G11" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="21" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="M11" s="21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="45" x14ac:dyDescent="0.2">
+      <c r="A12" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="23">
         <v>46266</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="D12" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="E12" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="F12" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="G12" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="H12" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="M12" s="22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="23">
+        <v>46266</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="K13" s="24">
+        <v>2</v>
+      </c>
+      <c r="L13" s="26">
+        <v>150000</v>
+      </c>
+      <c r="M13" s="27">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="13">
+        <v>46275</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="I14" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="J14" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="I12" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K12" s="12">
+      <c r="K14" s="24">
         <v>1</v>
       </c>
-      <c r="L12" s="14">
-        <v>1850000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="13">
-        <v>46266</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="K13" s="12">
-        <v>2</v>
-      </c>
-      <c r="L13" s="14">
+      <c r="L14" s="26">
+        <v>750000</v>
+      </c>
+      <c r="M14" s="26">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="30" x14ac:dyDescent="0.2">
+      <c r="A15" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="13">
+        <v>46275</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="K15" s="24">
+        <v>1</v>
+      </c>
+      <c r="L15" s="26">
         <v>150000</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="13">
-        <v>46275</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" s="12" t="s">
+      <c r="M15" s="26">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="30" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="K14" s="12">
-        <v>1</v>
-      </c>
-      <c r="L14" s="14">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="13">
-        <v>46275</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="K15" s="12">
-        <v>1</v>
-      </c>
-      <c r="L15" s="14">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="13">
+      <c r="C16" s="13">
         <v>46277</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="D16" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="E16" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="F16" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="G16" s="12" t="s">
         <v>61</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>62</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>63</v>
@@ -1710,316 +1758,100 @@
       <c r="J16" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="K16" s="12">
-        <v>3</v>
-      </c>
-      <c r="L16" s="14">
-        <v>350000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="13">
-        <v>46280</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="K17" s="12">
-        <v>10</v>
-      </c>
-      <c r="L17" s="14">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="13">
-        <v>46280</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="K18" s="12">
-        <v>2</v>
-      </c>
-      <c r="L18" s="14">
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="13">
-        <v>46283</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K19" s="12">
-        <v>1</v>
-      </c>
-      <c r="L19" s="14">
-        <v>375000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" s="13">
-        <v>46283</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="K20" s="12">
-        <v>5</v>
-      </c>
-      <c r="L20" s="14">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="13">
-        <v>46283</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="K21" s="12">
-        <v>1</v>
-      </c>
-      <c r="L21" s="14">
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="13">
-        <v>46285</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K22" s="12">
-        <v>2</v>
-      </c>
-      <c r="L22" s="14">
-        <v>1850000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="13">
-        <v>46285</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="H23" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="I23" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="J23" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="K23" s="21">
-        <v>1</v>
-      </c>
-      <c r="L23" s="22">
-        <v>750000</v>
-      </c>
+      <c r="K16" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16" s="14">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C25" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
@@ -2028,7 +1860,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
@@ -2037,18 +1869,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
       <c r="B8" s="16"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="18"/>
     </row>
   </sheetData>
@@ -2059,34 +1891,34 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
@@ -2095,7 +1927,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
@@ -2104,18 +1936,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
       <c r="B8" s="16"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="18"/>
     </row>
   </sheetData>
